--- a/Results_experiment/exp_2/preds_1111112222222222.xlsx
+++ b/Results_experiment/exp_2/preds_1111112222222222.xlsx
@@ -1596,7 +1596,7 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-0.7330690622329712</v>
+        <v>-0.910417377948761</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1610,7 +1610,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D3">
-        <v>1.294632196426392</v>
+        <v>1.55847692489624</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1624,7 +1624,7 @@
         <v>21.89999961853027</v>
       </c>
       <c r="D4">
-        <v>16.2808780670166</v>
+        <v>16.30044746398926</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1638,7 +1638,7 @@
         <v>25.89999961853027</v>
       </c>
       <c r="D5">
-        <v>16.70466804504395</v>
+        <v>15.17660713195801</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1652,7 +1652,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D6">
-        <v>-3.305689334869385</v>
+        <v>-2.622920274734497</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1666,7 +1666,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D7">
-        <v>5.074167251586914</v>
+        <v>4.527726173400879</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1680,7 +1680,7 @@
         <v>27.39999961853027</v>
       </c>
       <c r="D8">
-        <v>21.05036926269531</v>
+        <v>20.04736328125</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1694,7 +1694,7 @@
         <v>20.5</v>
       </c>
       <c r="D9">
-        <v>10.51680374145508</v>
+        <v>12.28870677947998</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1708,7 +1708,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D10">
-        <v>5.796936988830566</v>
+        <v>5.979835510253906</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1722,7 +1722,7 @@
         <v>33.09999847412109</v>
       </c>
       <c r="D11">
-        <v>22.51633644104004</v>
+        <v>21.82172393798828</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1736,7 +1736,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D12">
-        <v>4.450483798980713</v>
+        <v>4.417627334594727</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1750,7 +1750,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D13">
-        <v>0.8894545435905457</v>
+        <v>2.132473945617676</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1764,7 +1764,7 @@
         <v>-4</v>
       </c>
       <c r="D14">
-        <v>-3.03980016708374</v>
+        <v>-3.247481346130371</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1778,7 +1778,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D15">
-        <v>2.014183044433594</v>
+        <v>1.392493724822998</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1792,7 +1792,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D16">
-        <v>4.953235626220703</v>
+        <v>4.576874732971191</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1806,7 +1806,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D17">
-        <v>0.5770348310470581</v>
+        <v>0.6075752973556519</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1820,7 +1820,7 @@
         <v>12</v>
       </c>
       <c r="D18">
-        <v>8.835324287414551</v>
+        <v>3.957057952880859</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1834,7 +1834,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.4732502698898315</v>
+        <v>0.7477701902389526</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1848,7 +1848,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D20">
-        <v>-0.5207381844520569</v>
+        <v>-0.1440631747245789</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1862,7 +1862,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D21">
-        <v>4.544670581817627</v>
+        <v>6.331231117248535</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1876,7 +1876,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D22">
-        <v>0.3604712188243866</v>
+        <v>0.02241450548171997</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1890,7 +1890,7 @@
         <v>13.80000019073486</v>
       </c>
       <c r="D23">
-        <v>10.02948379516602</v>
+        <v>8.874747276306152</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1904,7 +1904,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D24">
-        <v>0.6840845346450806</v>
+        <v>0.4119403660297394</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1918,7 +1918,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D25">
-        <v>0.773935079574585</v>
+        <v>1.731239795684814</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1932,7 +1932,7 @@
         <v>37.90000152587891</v>
       </c>
       <c r="D26">
-        <v>27.55895805358887</v>
+        <v>33.25692749023438</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1946,7 +1946,7 @@
         <v>5.5</v>
       </c>
       <c r="D27">
-        <v>4.356847286224365</v>
+        <v>4.813494682312012</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1960,7 +1960,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D28">
-        <v>5.925628662109375</v>
+        <v>5.787005424499512</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1974,7 +1974,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D29">
-        <v>-3.105749130249023</v>
+        <v>-2.860435247421265</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1988,7 +1988,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D30">
-        <v>-0.4841707944869995</v>
+        <v>0.2637026906013489</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2002,7 +2002,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D31">
-        <v>3.098180770874023</v>
+        <v>3.664622068405151</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2016,7 +2016,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D32">
-        <v>0.3682662546634674</v>
+        <v>0.6721566915512085</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2030,7 +2030,7 @@
         <v>5.5</v>
       </c>
       <c r="D33">
-        <v>2.942181587219238</v>
+        <v>1.022588133811951</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2044,7 +2044,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D34">
-        <v>-2.283266544342041</v>
+        <v>-1.799555063247681</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2058,7 +2058,7 @@
         <v>4.5</v>
       </c>
       <c r="D35">
-        <v>5.239290714263916</v>
+        <v>4.917450904846191</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2072,7 +2072,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D36">
-        <v>-1.712682127952576</v>
+        <v>-1.270724058151245</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2086,7 +2086,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D37">
-        <v>0.1226301193237305</v>
+        <v>-0.06420332193374634</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2100,7 +2100,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D38">
-        <v>-0.182938814163208</v>
+        <v>0.3140507936477661</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2114,7 +2114,7 @@
         <v>0.5</v>
       </c>
       <c r="D39">
-        <v>0.5198741555213928</v>
+        <v>1.213669538497925</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2128,7 +2128,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D40">
-        <v>2.282341003417969</v>
+        <v>2.13853120803833</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2142,7 +2142,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D41">
-        <v>0.1211836338043213</v>
+        <v>-0.07726031541824341</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2156,7 +2156,7 @@
         <v>-10.10000038146973</v>
       </c>
       <c r="D42">
-        <v>-5.649617195129395</v>
+        <v>-4.374342918395996</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2170,7 +2170,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D43">
-        <v>0.4434814751148224</v>
+        <v>0.6962053179740906</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2184,7 +2184,7 @@
         <v>5</v>
       </c>
       <c r="D44">
-        <v>3.017502784729004</v>
+        <v>4.108821868896484</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2198,7 +2198,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D45">
-        <v>-2.271960258483887</v>
+        <v>-2.193856954574585</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2212,7 +2212,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D46">
-        <v>3.445678234100342</v>
+        <v>5.700051784515381</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2226,7 +2226,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D47">
-        <v>2.053015232086182</v>
+        <v>2.216870069503784</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2240,7 +2240,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D48">
-        <v>2.444793224334717</v>
+        <v>3.585900545120239</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2254,7 +2254,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D49">
-        <v>0.9106646776199341</v>
+        <v>1.136811971664429</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2268,7 +2268,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D50">
-        <v>6.263527870178223</v>
+        <v>5.133266448974609</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2282,7 +2282,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D51">
-        <v>3.812978744506836</v>
+        <v>3.612725257873535</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2296,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="D52">
-        <v>-0.605743408203125</v>
+        <v>-0.4076977372169495</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2310,7 +2310,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D53">
-        <v>1.188573598861694</v>
+        <v>1.171007394790649</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2324,7 +2324,7 @@
         <v>-5.5</v>
       </c>
       <c r="D54">
-        <v>-2.795479297637939</v>
+        <v>-2.822724580764771</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2338,7 +2338,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D55">
-        <v>0.8420771956443787</v>
+        <v>0.6016978621482849</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2352,7 +2352,7 @@
         <v>34</v>
       </c>
       <c r="D56">
-        <v>21.9385929107666</v>
+        <v>20.82268905639648</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2366,7 +2366,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D57">
-        <v>1.54965341091156</v>
+        <v>2.509087085723877</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2380,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="D58">
-        <v>2.467843055725098</v>
+        <v>2.149611234664917</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2394,7 +2394,7 @@
         <v>-3.5</v>
       </c>
       <c r="D59">
-        <v>-2.214698791503906</v>
+        <v>-1.68857479095459</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2408,7 +2408,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D60">
-        <v>-1.420918822288513</v>
+        <v>-0.7324389815330505</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2422,7 +2422,7 @@
         <v>6</v>
       </c>
       <c r="D61">
-        <v>0.8248905539512634</v>
+        <v>1.636682033538818</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2436,7 +2436,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D62">
-        <v>3.596105098724365</v>
+        <v>2.047956228256226</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2450,7 +2450,7 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>10.05527400970459</v>
+        <v>10.11554145812988</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2464,7 +2464,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D64">
-        <v>0.05655676126480103</v>
+        <v>0.1444257497787476</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2478,7 +2478,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D65">
-        <v>8.927508354187012</v>
+        <v>9.496285438537598</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2492,7 +2492,7 @@
         <v>28.20000076293945</v>
       </c>
       <c r="D66">
-        <v>16.62135124206543</v>
+        <v>15.47420024871826</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2506,7 +2506,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D67">
-        <v>4.509037971496582</v>
+        <v>5.463860034942627</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2520,7 +2520,7 @@
         <v>0.5</v>
       </c>
       <c r="D68">
-        <v>0.5678904056549072</v>
+        <v>0.7001153826713562</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2534,7 +2534,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D69">
-        <v>6.904796600341797</v>
+        <v>4.404840469360352</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2548,7 +2548,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D70">
-        <v>-1.659740328788757</v>
+        <v>-1.533907413482666</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2562,7 +2562,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D71">
-        <v>0.7793272733688354</v>
+        <v>0.4434332251548767</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2576,7 +2576,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D72">
-        <v>5.003232479095459</v>
+        <v>4.77310848236084</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2590,7 +2590,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D73">
-        <v>1.442141056060791</v>
+        <v>1.189753651618958</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2604,7 +2604,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D74">
-        <v>5.037965297698975</v>
+        <v>3.76488995552063</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2618,7 +2618,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D75">
-        <v>5.000233173370361</v>
+        <v>5.133973121643066</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0.2812548875808716</v>
+        <v>0.8408861756324768</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2646,7 +2646,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D77">
-        <v>0.5037235021591187</v>
+        <v>1.020296216011047</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2660,7 +2660,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D78">
-        <v>5.028970718383789</v>
+        <v>4.962961673736572</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2674,7 +2674,7 @@
         <v>9.5</v>
       </c>
       <c r="D79">
-        <v>5.010327816009521</v>
+        <v>4.978561401367188</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2688,7 +2688,7 @@
         <v>0.5</v>
       </c>
       <c r="D80">
-        <v>0.2824113965034485</v>
+        <v>0.2267071008682251</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2702,7 +2702,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D81">
-        <v>2.796607494354248</v>
+        <v>3.579053640365601</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2716,7 +2716,7 @@
         <v>1.5</v>
       </c>
       <c r="D82">
-        <v>0.02039754390716553</v>
+        <v>0.1651726365089417</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2730,7 +2730,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D83">
-        <v>0.6482323408126831</v>
+        <v>0.3244920372962952</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2744,7 +2744,7 @@
         <v>-1</v>
       </c>
       <c r="D84">
-        <v>0.202993631362915</v>
+        <v>2.947881460189819</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2758,7 +2758,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D85">
-        <v>2.149965763092041</v>
+        <v>2.680564641952515</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2772,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="D86">
-        <v>0.4732502698898315</v>
+        <v>0.0581936240196228</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2786,7 +2786,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D87">
-        <v>5.037626266479492</v>
+        <v>4.340470314025879</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2800,7 +2800,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D88">
-        <v>0.4565616250038147</v>
+        <v>0.42919921875</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2814,7 +2814,7 @@
         <v>15</v>
       </c>
       <c r="D89">
-        <v>13.53077602386475</v>
+        <v>11.19993114471436</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2828,7 +2828,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D90">
-        <v>6.369343757629395</v>
+        <v>5.30430793762207</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2842,7 +2842,7 @@
         <v>-14</v>
       </c>
       <c r="D91">
-        <v>-7.096468448638916</v>
+        <v>-8.903648376464844</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2856,7 +2856,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D92">
-        <v>1.401033043861389</v>
+        <v>1.165706634521484</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2870,7 +2870,7 @@
         <v>7.5</v>
       </c>
       <c r="D93">
-        <v>2.06154727935791</v>
+        <v>1.447449088096619</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2884,7 +2884,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D94">
-        <v>0.3711009621620178</v>
+        <v>0.3291963934898376</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2898,7 +2898,7 @@
         <v>-2</v>
       </c>
       <c r="D95">
-        <v>-2.166821002960205</v>
+        <v>-1.794990301132202</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2912,7 +2912,7 @@
         <v>15.5</v>
       </c>
       <c r="D96">
-        <v>9.046890258789062</v>
+        <v>8.369491577148438</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2926,7 +2926,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D97">
-        <v>-1.775891661643982</v>
+        <v>-1.802122354507446</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2940,7 +2940,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D98">
-        <v>20.82476234436035</v>
+        <v>18.02680206298828</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2954,7 +2954,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D99">
-        <v>-0.6273320913314819</v>
+        <v>-0.1638440489768982</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2968,7 +2968,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D100">
-        <v>0.6146765351295471</v>
+        <v>1.309206962585449</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2982,7 +2982,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D101">
-        <v>-1.453940033912659</v>
+        <v>-1.444825172424316</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2996,7 +2996,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D102">
-        <v>0.8045495748519897</v>
+        <v>1.48392391204834</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3010,7 +3010,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D103">
-        <v>3.853898525238037</v>
+        <v>9.357024192810059</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3024,7 +3024,7 @@
         <v>2</v>
       </c>
       <c r="D104">
-        <v>0.5049871206283569</v>
+        <v>1.58507764339447</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3038,7 +3038,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D105">
-        <v>2.787747859954834</v>
+        <v>4.789697170257568</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3052,7 +3052,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D106">
-        <v>-1.076951384544373</v>
+        <v>-0.8995104432106018</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3066,7 +3066,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D107">
-        <v>1.876486301422119</v>
+        <v>3.201109647750854</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3080,7 +3080,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D108">
-        <v>4.601836204528809</v>
+        <v>4.206067562103271</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3094,7 +3094,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D109">
-        <v>-2.812270641326904</v>
+        <v>-1.290842294692993</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3108,7 +3108,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D110">
-        <v>0.1021257638931274</v>
+        <v>0.1155180335044861</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3122,7 +3122,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D111">
-        <v>2.570656776428223</v>
+        <v>0.046764075756073</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3136,7 +3136,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D112">
-        <v>1.42107105255127</v>
+        <v>3.504308462142944</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3150,7 +3150,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D113">
-        <v>0.3694549798965454</v>
+        <v>0.2561136484146118</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3164,7 +3164,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D114">
-        <v>4.293053150177002</v>
+        <v>4.419400691986084</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3178,7 +3178,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D115">
-        <v>1.569853901863098</v>
+        <v>1.785341024398804</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3192,7 +3192,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D116">
-        <v>-1.028816103935242</v>
+        <v>-1.348860025405884</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3206,7 +3206,7 @@
         <v>2</v>
       </c>
       <c r="D117">
-        <v>-2.973040103912354</v>
+        <v>-2.230994939804077</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3220,7 +3220,7 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>1.09711766242981</v>
+        <v>1.82589054107666</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3234,7 +3234,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D119">
-        <v>-0.6724740266799927</v>
+        <v>-0.2083727717399597</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3248,7 +3248,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D120">
-        <v>7.838903427124023</v>
+        <v>8.388647079467773</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3262,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="D121">
-        <v>0.4732502698898315</v>
+        <v>0.6836756467819214</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3276,7 +3276,7 @@
         <v>31.39999961853027</v>
       </c>
       <c r="D122">
-        <v>22.16450500488281</v>
+        <v>20.57489967346191</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3290,7 +3290,7 @@
         <v>-6.800000190734863</v>
       </c>
       <c r="D123">
-        <v>-1.168200612068176</v>
+        <v>-0.887769877910614</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3304,7 +3304,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D124">
-        <v>1.212950706481934</v>
+        <v>2.060975551605225</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3318,7 +3318,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D125">
-        <v>-0.1500785946846008</v>
+        <v>-0.2153266072273254</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3332,7 +3332,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D126">
-        <v>-0.003803163766860962</v>
+        <v>-0.2028642892837524</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3346,7 +3346,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D127">
-        <v>4.261799335479736</v>
+        <v>5.826609134674072</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3360,7 +3360,7 @@
         <v>2</v>
       </c>
       <c r="D128">
-        <v>-0.3766006231307983</v>
+        <v>0.03997188806533813</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3374,7 +3374,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D129">
-        <v>0.9606383442878723</v>
+        <v>0.9572532773017883</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3388,7 +3388,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D130">
-        <v>-0.1447596549987793</v>
+        <v>1.478936433792114</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3402,7 +3402,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D131">
-        <v>0.07239556312561035</v>
+        <v>-0.1710878610610962</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3416,7 +3416,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D132">
-        <v>4.682675838470459</v>
+        <v>3.51176381111145</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3430,7 +3430,7 @@
         <v>1.5</v>
       </c>
       <c r="D133">
-        <v>2.283077955245972</v>
+        <v>2.028271913528442</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3444,7 +3444,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D134">
-        <v>0.9085392951965332</v>
+        <v>0.1580333113670349</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3458,7 +3458,7 @@
         <v>3.5</v>
       </c>
       <c r="D135">
-        <v>0.3977070450782776</v>
+        <v>0.08561491966247559</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3472,7 +3472,7 @@
         <v>-8.199999809265137</v>
       </c>
       <c r="D136">
-        <v>-3.091848373413086</v>
+        <v>-3.184770822525024</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3486,7 +3486,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D137">
-        <v>3.031095027923584</v>
+        <v>3.395553350448608</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3500,7 +3500,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D138">
-        <v>-0.2036376595497131</v>
+        <v>-0.7751098275184631</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3514,7 +3514,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D139">
-        <v>0.4323264956474304</v>
+        <v>0.1234574913978577</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3528,7 +3528,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D140">
-        <v>0.8590344786643982</v>
+        <v>1.554677486419678</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3542,7 +3542,7 @@
         <v>6</v>
       </c>
       <c r="D141">
-        <v>6.815625190734863</v>
+        <v>6.319670677185059</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3556,7 +3556,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D142">
-        <v>-0.2075909376144409</v>
+        <v>-0.3112364411354065</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3570,7 +3570,7 @@
         <v>4</v>
       </c>
       <c r="D143">
-        <v>1.04979419708252</v>
+        <v>0.9637198448181152</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3584,7 +3584,7 @@
         <v>-3</v>
       </c>
       <c r="D144">
-        <v>0.02032050490379333</v>
+        <v>-0.3500819802284241</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3598,7 +3598,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D145">
-        <v>7.170596599578857</v>
+        <v>6.346432685852051</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3612,7 +3612,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D146">
-        <v>1.102581024169922</v>
+        <v>1.246045112609863</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3626,7 +3626,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D147">
-        <v>0.315462052822113</v>
+        <v>0.1288944482803345</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3640,7 +3640,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D148">
-        <v>2.292054176330566</v>
+        <v>2.952074766159058</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3654,7 +3654,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D149">
-        <v>6.197751045227051</v>
+        <v>5.528605461120605</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3668,7 +3668,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D150">
-        <v>0.442472904920578</v>
+        <v>0.2583032250404358</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3682,7 +3682,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D151">
-        <v>6.475312232971191</v>
+        <v>6.705528736114502</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3696,7 +3696,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D152">
-        <v>-1.414529919624329</v>
+        <v>-0.937139093875885</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3710,7 +3710,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D153">
-        <v>6.843349933624268</v>
+        <v>7.48591423034668</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3724,7 +3724,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D154">
-        <v>-0.2038353085517883</v>
+        <v>-0.5032952427864075</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3738,7 +3738,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D155">
-        <v>0.07972517609596252</v>
+        <v>0.06305581331253052</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3752,7 +3752,7 @@
         <v>8</v>
       </c>
       <c r="D156">
-        <v>0.9967091679573059</v>
+        <v>0.8218685984611511</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3766,7 +3766,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D157">
-        <v>4.683016777038574</v>
+        <v>6.099533081054688</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3780,7 +3780,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D158">
-        <v>0.6109363436698914</v>
+        <v>0.3928055465221405</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3794,7 +3794,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D159">
-        <v>-0.5302609205245972</v>
+        <v>-0.5584352612495422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3808,7 +3808,7 @@
         <v>-9</v>
       </c>
       <c r="D160">
-        <v>-0.1939489245414734</v>
+        <v>0.4712377488613129</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3822,7 +3822,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D161">
-        <v>1.833772778511047</v>
+        <v>1.078128814697266</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3836,7 +3836,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D162">
-        <v>-0.2536991238594055</v>
+        <v>-0.4573014378547668</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3850,7 +3850,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D163">
-        <v>4.565544128417969</v>
+        <v>4.498758316040039</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3864,7 +3864,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D164">
-        <v>-0.1115033030509949</v>
+        <v>-0.9605064988136292</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3878,7 +3878,7 @@
         <v>-2</v>
       </c>
       <c r="D165">
-        <v>-0.6753352880477905</v>
+        <v>-0.04764729738235474</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3892,7 +3892,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D166">
-        <v>4.273294925689697</v>
+        <v>4.370116233825684</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3906,7 +3906,7 @@
         <v>-4.5</v>
       </c>
       <c r="D167">
-        <v>-2.491996765136719</v>
+        <v>-2.510163068771362</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3920,7 +3920,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D168">
-        <v>0.8953675627708435</v>
+        <v>0.9481056332588196</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3934,7 +3934,7 @@
         <v>3.5</v>
       </c>
       <c r="D169">
-        <v>0.4443138837814331</v>
+        <v>0.5643298625946045</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3948,7 +3948,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D170">
-        <v>-0.9143966436386108</v>
+        <v>-0.4312580227851868</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3962,7 +3962,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D171">
-        <v>0.7890815734863281</v>
+        <v>0.4610062837600708</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3976,7 +3976,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D172">
-        <v>4.514427661895752</v>
+        <v>4.327500343322754</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3990,7 +3990,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D173">
-        <v>-2.591373920440674</v>
+        <v>-1.52005410194397</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4004,7 +4004,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D174">
-        <v>4.956428527832031</v>
+        <v>4.32179069519043</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4018,7 +4018,7 @@
         <v>2</v>
       </c>
       <c r="D175">
-        <v>0.8615769147872925</v>
+        <v>1.012436866760254</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4032,7 +4032,7 @@
         <v>-9.300000190734863</v>
       </c>
       <c r="D176">
-        <v>-2.765871524810791</v>
+        <v>-3.15538477897644</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4046,7 +4046,7 @@
         <v>-3</v>
       </c>
       <c r="D177">
-        <v>-2.309847354888916</v>
+        <v>-2.339977979660034</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4060,7 +4060,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D178">
-        <v>5.476099967956543</v>
+        <v>5.738649368286133</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4074,7 +4074,7 @@
         <v>28.39999961853027</v>
       </c>
       <c r="D179">
-        <v>14.46730422973633</v>
+        <v>14.8656177520752</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4088,7 +4088,7 @@
         <v>3</v>
       </c>
       <c r="D180">
-        <v>0.5166931748390198</v>
+        <v>1.260460376739502</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4102,7 +4102,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D181">
-        <v>7.657279014587402</v>
+        <v>6.889796257019043</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4116,7 +4116,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D182">
-        <v>-3.366090774536133</v>
+        <v>-2.915139675140381</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4130,7 +4130,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D183">
-        <v>-4.445656776428223</v>
+        <v>-4.062569618225098</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4144,7 +4144,7 @@
         <v>8</v>
       </c>
       <c r="D184">
-        <v>5.308962821960449</v>
+        <v>4.266484260559082</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4158,7 +4158,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D185">
-        <v>0.837049663066864</v>
+        <v>1.348229646682739</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4172,7 +4172,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D186">
-        <v>3.472660064697266</v>
+        <v>2.539954662322998</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4186,7 +4186,7 @@
         <v>-3</v>
       </c>
       <c r="D187">
-        <v>0.482423722743988</v>
+        <v>0.6229013800621033</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4200,7 +4200,7 @@
         <v>4</v>
       </c>
       <c r="D188">
-        <v>0.4654815495014191</v>
+        <v>1.025842189788818</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4214,7 +4214,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D189">
-        <v>0.9909731149673462</v>
+        <v>0.6652780175209045</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4228,7 +4228,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D190">
-        <v>0.6858187913894653</v>
+        <v>0.3767085075378418</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4242,7 +4242,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D191">
-        <v>0.6783753633499146</v>
+        <v>0.7845379114151001</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4256,7 +4256,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D192">
-        <v>11.40176868438721</v>
+        <v>9.528811454772949</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4270,7 +4270,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D193">
-        <v>6.483599662780762</v>
+        <v>5.804750442504883</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4284,7 +4284,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D194">
-        <v>0.4017332196235657</v>
+        <v>1.427062511444092</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4298,7 +4298,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D195">
-        <v>0.492912769317627</v>
+        <v>0.3813046813011169</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4312,7 +4312,7 @@
         <v>17.39999961853027</v>
       </c>
       <c r="D196">
-        <v>13.60486125946045</v>
+        <v>12.3220911026001</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4326,7 +4326,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D197">
-        <v>5.083277702331543</v>
+        <v>5.200895309448242</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4340,7 +4340,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D198">
-        <v>0.441907525062561</v>
+        <v>0.2576407790184021</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4354,7 +4354,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D199">
-        <v>4.295069694519043</v>
+        <v>5.876572132110596</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4368,7 +4368,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D200">
-        <v>0.4897964298725128</v>
+        <v>0.5248309969902039</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4382,7 +4382,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D201">
-        <v>-0.638542652130127</v>
+        <v>-1.147220849990845</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4396,7 +4396,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D202">
-        <v>-0.9738279581069946</v>
+        <v>-0.931856095790863</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4410,7 +4410,7 @@
         <v>1.5</v>
       </c>
       <c r="D203">
-        <v>0.2326420396566391</v>
+        <v>0.5693666934967041</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4424,7 +4424,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D204">
-        <v>2.777382373809814</v>
+        <v>2.206676244735718</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4438,7 +4438,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D205">
-        <v>0.862823486328125</v>
+        <v>0.7150424122810364</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4452,7 +4452,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D206">
-        <v>10.56911945343018</v>
+        <v>9.147883415222168</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4466,7 +4466,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D207">
-        <v>-0.7942336797714233</v>
+        <v>-0.8958467841148376</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4480,7 +4480,7 @@
         <v>3.5</v>
       </c>
       <c r="D208">
-        <v>2.715644836425781</v>
+        <v>1.916423320770264</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4494,7 +4494,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D209">
-        <v>-2.227953910827637</v>
+        <v>-0.9683342576026917</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4508,7 +4508,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D210">
-        <v>-1.929295182228088</v>
+        <v>-1.69072413444519</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4522,7 +4522,7 @@
         <v>3.5</v>
       </c>
       <c r="D211">
-        <v>0.5652934312820435</v>
+        <v>1.024099588394165</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4536,7 +4536,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D212">
-        <v>2.085651397705078</v>
+        <v>2.063101053237915</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4550,7 +4550,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D213">
-        <v>3.021763801574707</v>
+        <v>2.889597177505493</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4564,7 +4564,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D214">
-        <v>0.4798280894756317</v>
+        <v>0.2514740526676178</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4578,7 +4578,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D215">
-        <v>-0.9438925981521606</v>
+        <v>-0.08688497543334961</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4592,7 +4592,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D216">
-        <v>1.902569651603699</v>
+        <v>1.515223026275635</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>-1.109567046165466</v>
+        <v>-0.3264248967170715</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4620,7 +4620,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D218">
-        <v>-0.7306724786758423</v>
+        <v>-0.9863950610160828</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4634,7 +4634,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D219">
-        <v>2.515408992767334</v>
+        <v>2.249824047088623</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4648,7 +4648,7 @@
         <v>-1.5</v>
       </c>
       <c r="D220">
-        <v>-1.986015915870667</v>
+        <v>-1.217646837234497</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4662,7 +4662,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D221">
-        <v>4.447517395019531</v>
+        <v>4.269275665283203</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4676,7 +4676,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D222">
-        <v>-1.621936440467834</v>
+        <v>-1.537688970565796</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4690,7 +4690,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D223">
-        <v>-3.146575450897217</v>
+        <v>-2.441321611404419</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4704,7 +4704,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D224">
-        <v>-0.6261471509933472</v>
+        <v>0.06337124109268188</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4718,7 +4718,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D225">
-        <v>-0.2012598514556885</v>
+        <v>0.03274023532867432</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4732,7 +4732,7 @@
         <v>2</v>
       </c>
       <c r="D226">
-        <v>1.064631700515747</v>
+        <v>0.6917276978492737</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4746,7 +4746,7 @@
         <v>0.5</v>
       </c>
       <c r="D227">
-        <v>-0.3947539925575256</v>
+        <v>-1.52875804901123</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4760,7 +4760,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D228">
-        <v>-0.151736855506897</v>
+        <v>0.7394672632217407</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4774,7 +4774,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D229">
-        <v>4.77900505065918</v>
+        <v>5.988083362579346</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="D230">
-        <v>0.3672906160354614</v>
+        <v>0.9848490357398987</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4802,7 +4802,7 @@
         <v>-1</v>
       </c>
       <c r="D231">
-        <v>-1.208980441093445</v>
+        <v>-0.8415419459342957</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4816,7 +4816,7 @@
         <v>25</v>
       </c>
       <c r="D232">
-        <v>17.69585609436035</v>
+        <v>16.10131454467773</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4830,7 +4830,7 @@
         <v>0.5</v>
       </c>
       <c r="D233">
-        <v>1.547643542289734</v>
+        <v>1.597482919692993</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4844,7 +4844,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D234">
-        <v>0.7316096425056458</v>
+        <v>0.6638146638870239</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4858,7 +4858,7 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>14.29484844207764</v>
+        <v>15.30154895782471</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4872,7 +4872,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D236">
-        <v>-2.802898406982422</v>
+        <v>-4.160711288452148</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4886,7 +4886,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D237">
-        <v>0.4658552408218384</v>
+        <v>0.5864608883857727</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4900,7 +4900,7 @@
         <v>20.5</v>
       </c>
       <c r="D238">
-        <v>17.59711456298828</v>
+        <v>17.58718299865723</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4914,7 +4914,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D239">
-        <v>0.2302421778440475</v>
+        <v>0.2189314067363739</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4928,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="D240">
-        <v>0.521508514881134</v>
+        <v>0.3443458676338196</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4942,7 +4942,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D241">
-        <v>-1.201899409294128</v>
+        <v>-0.8341558575630188</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4956,7 +4956,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D242">
-        <v>-1.978435873985291</v>
+        <v>-1.620997667312622</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4970,7 +4970,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D243">
-        <v>0.5494515299797058</v>
+        <v>0.7172227501869202</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4984,7 +4984,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D244">
-        <v>0.2339306771755219</v>
+        <v>-0.5799615979194641</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4998,7 +4998,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D245">
-        <v>0.8288143873214722</v>
+        <v>0.8699942231178284</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5012,7 +5012,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D246">
-        <v>0.3860026299953461</v>
+        <v>1.613289594650269</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5026,7 +5026,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D247">
-        <v>0.4335001409053802</v>
+        <v>1.133821964263916</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5040,7 +5040,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D248">
-        <v>-0.5442260503768921</v>
+        <v>-1.161623954772949</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5054,7 +5054,7 @@
         <v>-22.60000038146973</v>
       </c>
       <c r="D249">
-        <v>-6.574796676635742</v>
+        <v>-5.757352828979492</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5068,7 +5068,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D250">
-        <v>-2.53897762298584</v>
+        <v>-2.783645391464233</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5082,7 +5082,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D251">
-        <v>4.253043174743652</v>
+        <v>3.664106845855713</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5096,7 +5096,7 @@
         <v>3.5</v>
       </c>
       <c r="D252">
-        <v>1.43484103679657</v>
+        <v>2.544953584671021</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5110,7 +5110,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D253">
-        <v>0.6712414622306824</v>
+        <v>0.4675013422966003</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5124,7 +5124,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D254">
-        <v>-1.486766219139099</v>
+        <v>-1.992685556411743</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5138,7 +5138,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D255">
-        <v>4.645501613616943</v>
+        <v>5.648228645324707</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5152,7 +5152,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D256">
-        <v>-0.8631693124771118</v>
+        <v>-1.194595336914062</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5166,7 +5166,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D257">
-        <v>-0.2344435453414917</v>
+        <v>-0.0859643816947937</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5180,7 +5180,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D258">
-        <v>-0.1667859554290771</v>
+        <v>-0.2221084237098694</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5194,7 +5194,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D259">
-        <v>0.6631057262420654</v>
+        <v>0.5436714291572571</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5208,7 +5208,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D260">
-        <v>-1.632316946983337</v>
+        <v>-0.76036137342453</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5222,7 +5222,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D261">
-        <v>0.543576180934906</v>
+        <v>0.6139557957649231</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5236,7 +5236,7 @@
         <v>-1</v>
       </c>
       <c r="D262">
-        <v>0.412423849105835</v>
+        <v>0.07026249170303345</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5250,7 +5250,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D263">
-        <v>4.172828674316406</v>
+        <v>3.349426507949829</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5264,7 +5264,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D264">
-        <v>2.080500602722168</v>
+        <v>2.734689950942993</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5278,7 +5278,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D265">
-        <v>1.473889589309692</v>
+        <v>2.225070953369141</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5292,7 +5292,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D266">
-        <v>2.822474956512451</v>
+        <v>2.121878623962402</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5306,7 +5306,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D267">
-        <v>1.13901686668396</v>
+        <v>0.6137706637382507</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5320,7 +5320,7 @@
         <v>37.20000076293945</v>
       </c>
       <c r="D268">
-        <v>20.6462230682373</v>
+        <v>22.0317268371582</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5334,7 +5334,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D269">
-        <v>-1.217844486236572</v>
+        <v>-1.632081747055054</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5348,7 +5348,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D270">
-        <v>2.010425090789795</v>
+        <v>2.822083473205566</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5362,7 +5362,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D271">
-        <v>1.895661473274231</v>
+        <v>1.729703664779663</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5376,7 +5376,7 @@
         <v>1.5</v>
       </c>
       <c r="D272">
-        <v>0.114590048789978</v>
+        <v>0.9743412137031555</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5390,7 +5390,7 @@
         <v>-0.5</v>
       </c>
       <c r="D273">
-        <v>1.31646740436554</v>
+        <v>0.7138488292694092</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5404,7 +5404,7 @@
         <v>-12.30000019073486</v>
       </c>
       <c r="D274">
-        <v>-4.251206398010254</v>
+        <v>-6.053255558013916</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5418,7 +5418,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D275">
-        <v>-0.5273276567459106</v>
+        <v>-0.6524046063423157</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5432,7 +5432,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D276">
-        <v>3.886021137237549</v>
+        <v>5.427525043487549</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5446,7 +5446,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D277">
-        <v>0.8683034777641296</v>
+        <v>1.930722951889038</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5460,7 +5460,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D278">
-        <v>5.751283168792725</v>
+        <v>6.671905517578125</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5474,7 +5474,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D279">
-        <v>-1.31978714466095</v>
+        <v>-1.6455979347229</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5488,7 +5488,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D280">
-        <v>1.538000345230103</v>
+        <v>1.670398473739624</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5502,7 +5502,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D281">
-        <v>7.906201362609863</v>
+        <v>8.470741271972656</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5516,7 +5516,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D282">
-        <v>10.77866649627686</v>
+        <v>10.68369674682617</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5530,7 +5530,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D283">
-        <v>0.7304811477661133</v>
+        <v>1.31146764755249</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5544,7 +5544,7 @@
         <v>5</v>
       </c>
       <c r="D284">
-        <v>5.156942367553711</v>
+        <v>4.776474952697754</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5558,7 +5558,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D285">
-        <v>0.7213062047958374</v>
+        <v>0.5733675956726074</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5572,7 +5572,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D286">
-        <v>0.7825384140014648</v>
+        <v>1.409376382827759</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5586,7 +5586,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D287">
-        <v>3.856428623199463</v>
+        <v>5.211157321929932</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5600,7 +5600,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D288">
-        <v>4.689796447753906</v>
+        <v>5.713152408599854</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5614,7 +5614,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D289">
-        <v>-0.1573796272277832</v>
+        <v>2.113673210144043</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5628,7 +5628,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D290">
-        <v>7.186907291412354</v>
+        <v>7.347274780273438</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5642,7 +5642,7 @@
         <v>2.5</v>
       </c>
       <c r="D291">
-        <v>-1.935596346855164</v>
+        <v>-0.9889374375343323</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5656,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>0.6202260851860046</v>
+        <v>2.190478324890137</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5670,7 +5670,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D293">
-        <v>-2.580292701721191</v>
+        <v>-1.683255434036255</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5684,7 +5684,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D294">
-        <v>3.786181926727295</v>
+        <v>4.2386794090271</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5698,7 +5698,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D295">
-        <v>4.069524765014648</v>
+        <v>3.805710077285767</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5712,7 +5712,7 @@
         <v>6</v>
       </c>
       <c r="D296">
-        <v>1.639087319374084</v>
+        <v>2.229254484176636</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5726,7 +5726,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D297">
-        <v>-2.419634342193604</v>
+        <v>-1.572011470794678</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5740,7 +5740,7 @@
         <v>9.5</v>
       </c>
       <c r="D298">
-        <v>11.9198579788208</v>
+        <v>11.35072231292725</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5754,7 +5754,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D299">
-        <v>0.5937756896018982</v>
+        <v>0.744086742401123</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5768,7 +5768,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D300">
-        <v>3.142196655273438</v>
+        <v>5.002592086791992</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5782,7 +5782,7 @@
         <v>9</v>
       </c>
       <c r="D301">
-        <v>1.631640076637268</v>
+        <v>1.828344821929932</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5796,7 +5796,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D302">
-        <v>1.213542342185974</v>
+        <v>2.347182512283325</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5810,7 +5810,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D303">
-        <v>0.5249292850494385</v>
+        <v>0.2021871209144592</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5824,7 +5824,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D304">
-        <v>-0.1744986772537231</v>
+        <v>-0.3439375758171082</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5838,7 +5838,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D305">
-        <v>-0.9403172731399536</v>
+        <v>-1.443289041519165</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5852,7 +5852,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D306">
-        <v>-2.808091163635254</v>
+        <v>-2.917611837387085</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5866,7 +5866,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D307">
-        <v>4.870022773742676</v>
+        <v>5.0780029296875</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5880,7 +5880,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D308">
-        <v>0.5805041193962097</v>
+        <v>0.5070273876190186</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5894,7 +5894,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D309">
-        <v>0.4829533398151398</v>
+        <v>0.692091166973114</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5908,7 +5908,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D310">
-        <v>-1.86916983127594</v>
+        <v>-1.371358156204224</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5922,7 +5922,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D311">
-        <v>1.286840677261353</v>
+        <v>1.849318504333496</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5936,7 +5936,7 @@
         <v>-2.5</v>
       </c>
       <c r="D312">
-        <v>-2.257112503051758</v>
+        <v>-2.18252420425415</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5950,7 +5950,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D313">
-        <v>0.8184967041015625</v>
+        <v>1.359732389450073</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5964,7 +5964,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D314">
-        <v>-0.4945429563522339</v>
+        <v>-0.04130274057388306</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5978,7 +5978,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D315">
-        <v>0.829552948474884</v>
+        <v>0.8816431760787964</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5992,7 +5992,7 @@
         <v>1</v>
       </c>
       <c r="D316">
-        <v>0.4411218464374542</v>
+        <v>-0.6618784070014954</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6006,7 +6006,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D317">
-        <v>0.5651006698608398</v>
+        <v>0.5087608098983765</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6020,7 +6020,7 @@
         <v>-8.5</v>
       </c>
       <c r="D318">
-        <v>-2.330946445465088</v>
+        <v>-2.264073610305786</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6034,7 +6034,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D319">
-        <v>4.816685676574707</v>
+        <v>3.607235193252563</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6048,7 +6048,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D320">
-        <v>7.677316665649414</v>
+        <v>6.566306114196777</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6062,7 +6062,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D321">
-        <v>9.313458442687988</v>
+        <v>8.889150619506836</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -6076,7 +6076,7 @@
         <v>-4</v>
       </c>
       <c r="D322">
-        <v>1.006442666053772</v>
+        <v>1.82758355140686</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6090,7 +6090,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D323">
-        <v>0.7590073347091675</v>
+        <v>1.774833917617798</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6104,7 +6104,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D324">
-        <v>9.132651329040527</v>
+        <v>8.716704368591309</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6118,7 +6118,7 @@
         <v>17.89999961853027</v>
       </c>
       <c r="D325">
-        <v>13.011155128479</v>
+        <v>12.93536853790283</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6132,7 +6132,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D326">
-        <v>3.17638111114502</v>
+        <v>2.860556840896606</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6146,7 +6146,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D327">
-        <v>1.619577646255493</v>
+        <v>2.305672645568848</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6160,7 +6160,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D328">
-        <v>2.309623241424561</v>
+        <v>3.446658849716187</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6174,7 +6174,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D329">
-        <v>1.546103596687317</v>
+        <v>0.6276842355728149</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6188,7 +6188,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D330">
-        <v>2.226665735244751</v>
+        <v>3.188571453094482</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6202,7 +6202,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D331">
-        <v>-0.08841276168823242</v>
+        <v>-0.06400978565216064</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6216,7 +6216,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D332">
-        <v>-0.1439175605773926</v>
+        <v>0.6615477800369263</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6230,7 +6230,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D333">
-        <v>2.261621952056885</v>
+        <v>3.495204210281372</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6244,7 +6244,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D334">
-        <v>-1.674265027046204</v>
+        <v>-1.983172178268433</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6258,7 +6258,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D335">
-        <v>-1.102963447570801</v>
+        <v>-0.8663223385810852</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6272,7 +6272,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D336">
-        <v>0.3059929609298706</v>
+        <v>-0.3429974913597107</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6286,7 +6286,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D337">
-        <v>0.619504451751709</v>
+        <v>0.02011281251907349</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6300,7 +6300,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D338">
-        <v>-0.3176626563072205</v>
+        <v>-0.7609707713127136</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6314,7 +6314,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D339">
-        <v>-1.844564080238342</v>
+        <v>-1.408100366592407</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6328,7 +6328,7 @@
         <v>23.20000076293945</v>
       </c>
       <c r="D340">
-        <v>11.30220317840576</v>
+        <v>9.972697257995605</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6342,7 +6342,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D341">
-        <v>-1.841764092445374</v>
+        <v>0.3917888700962067</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6356,7 +6356,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D342">
-        <v>0.8202271461486816</v>
+        <v>1.115918517112732</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6370,7 +6370,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D343">
-        <v>0.05653214454650879</v>
+        <v>0.6345270276069641</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6384,7 +6384,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D344">
-        <v>0.6025322079658508</v>
+        <v>0.7124238610267639</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6398,7 +6398,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D345">
-        <v>0.5124509334564209</v>
+        <v>0.7798298597335815</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6412,7 +6412,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D346">
-        <v>6.674213409423828</v>
+        <v>6.755575180053711</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6426,7 +6426,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D347">
-        <v>3.872109889984131</v>
+        <v>5.027909278869629</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6440,7 +6440,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D348">
-        <v>1.946637272834778</v>
+        <v>2.473474264144897</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6454,7 +6454,7 @@
         <v>-3</v>
       </c>
       <c r="D349">
-        <v>0.7683405876159668</v>
+        <v>0.6331733465194702</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6468,7 +6468,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D350">
-        <v>0.9636121392250061</v>
+        <v>1.566124558448792</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6482,7 +6482,7 @@
         <v>-8.699999809265137</v>
       </c>
       <c r="D351">
-        <v>-0.6479882001876831</v>
+        <v>-0.1306338310241699</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6496,7 +6496,7 @@
         <v>-0.5</v>
       </c>
       <c r="D352">
-        <v>-0.01642030477523804</v>
+        <v>-0.1017472743988037</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6510,7 +6510,7 @@
         <v>-9.300000190734863</v>
       </c>
       <c r="D353">
-        <v>-3.934260368347168</v>
+        <v>-2.619682788848877</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6524,7 +6524,7 @@
         <v>3.5</v>
       </c>
       <c r="D354">
-        <v>1.106698513031006</v>
+        <v>1.528609991073608</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6538,7 +6538,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D355">
-        <v>1.164438366889954</v>
+        <v>2.762844562530518</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6552,7 +6552,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D356">
-        <v>2.599024772644043</v>
+        <v>0.6074872016906738</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6566,7 +6566,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D357">
-        <v>5.182077884674072</v>
+        <v>3.205912113189697</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6580,7 +6580,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D358">
-        <v>0.2535563111305237</v>
+        <v>-0.05732715129852295</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6594,7 +6594,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D359">
-        <v>-0.1787582635879517</v>
+        <v>0.09256333112716675</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6608,7 +6608,7 @@
         <v>-1</v>
       </c>
       <c r="D360">
-        <v>-0.9977990388870239</v>
+        <v>-1.574183464050293</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6622,7 +6622,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D361">
-        <v>-1.311827778816223</v>
+        <v>-0.7631413340568542</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6636,7 +6636,7 @@
         <v>4.5</v>
       </c>
       <c r="D362">
-        <v>2.46690845489502</v>
+        <v>3.580129861831665</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6650,7 +6650,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D363">
-        <v>1.053157687187195</v>
+        <v>2.405868053436279</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6664,7 +6664,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D364">
-        <v>0.731715202331543</v>
+        <v>0.8652080297470093</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6678,7 +6678,7 @@
         <v>35.09999847412109</v>
       </c>
       <c r="D365">
-        <v>27.27156639099121</v>
+        <v>22.21853065490723</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6692,7 +6692,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D366">
-        <v>0.3188423812389374</v>
+        <v>0.8680268526077271</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6706,7 +6706,7 @@
         <v>4</v>
       </c>
       <c r="D367">
-        <v>0.4732502698898315</v>
+        <v>0.8483239412307739</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6720,7 +6720,7 @@
         <v>2</v>
       </c>
       <c r="D368">
-        <v>0.8997810482978821</v>
+        <v>0.9390974044799805</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6734,7 +6734,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D369">
-        <v>2.038302421569824</v>
+        <v>4.285739421844482</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6748,7 +6748,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D370">
-        <v>1.443734288215637</v>
+        <v>1.678290367126465</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6762,7 +6762,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D371">
-        <v>-0.726015567779541</v>
+        <v>-1.773445844650269</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6776,7 +6776,7 @@
         <v>-2.5</v>
       </c>
       <c r="D372">
-        <v>-1.035420656204224</v>
+        <v>-1.413124322891235</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6790,7 +6790,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D373">
-        <v>0.6994427442550659</v>
+        <v>0.9101396799087524</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6804,7 +6804,7 @@
         <v>-1.5</v>
       </c>
       <c r="D374">
-        <v>-3.857901573181152</v>
+        <v>-3.561094522476196</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6818,7 +6818,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D375">
-        <v>-5.209582328796387</v>
+        <v>-4.426274299621582</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6832,7 +6832,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D376">
-        <v>5.016815185546875</v>
+        <v>4.932130813598633</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6846,7 +6846,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D377">
-        <v>5.437732696533203</v>
+        <v>4.535649299621582</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6860,7 +6860,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D378">
-        <v>0.4436549842357635</v>
+        <v>0.405876487493515</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6874,7 +6874,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D379">
-        <v>-2.029805660247803</v>
+        <v>-0.5723727345466614</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6888,7 +6888,7 @@
         <v>2.5</v>
       </c>
       <c r="D380">
-        <v>-0.3803231120109558</v>
+        <v>-0.3509159684181213</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6902,7 +6902,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D381">
-        <v>0.236799418926239</v>
+        <v>0.4513474106788635</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6916,7 +6916,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D382">
-        <v>3.994414329528809</v>
+        <v>4.264801502227783</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6930,7 +6930,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D383">
-        <v>2.143702030181885</v>
+        <v>1.38902759552002</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6944,7 +6944,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D384">
-        <v>0.6866226196289062</v>
+        <v>1.291122674942017</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6958,7 +6958,7 @@
         <v>25.10000038146973</v>
       </c>
       <c r="D385">
-        <v>21.9279899597168</v>
+        <v>20.41172981262207</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6972,7 +6972,7 @@
         <v>4.5</v>
       </c>
       <c r="D386">
-        <v>1.338952302932739</v>
+        <v>2.000714063644409</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6986,7 +6986,7 @@
         <v>8</v>
       </c>
       <c r="D387">
-        <v>5.695104598999023</v>
+        <v>4.821871280670166</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7000,7 +7000,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D388">
-        <v>2.022868156433105</v>
+        <v>0.255332887172699</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7014,7 +7014,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D389">
-        <v>-0.0134279727935791</v>
+        <v>-0.103586733341217</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7028,7 +7028,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D390">
-        <v>-0.1799353361129761</v>
+        <v>-0.3848548531532288</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -7042,7 +7042,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D391">
-        <v>5.993390083312988</v>
+        <v>6.166279792785645</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -7056,7 +7056,7 @@
         <v>19</v>
       </c>
       <c r="D392">
-        <v>18.52304077148438</v>
+        <v>15.8552827835083</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -7070,7 +7070,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D393">
-        <v>0.1072011291980743</v>
+        <v>0.316238135099411</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -7084,7 +7084,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D394">
-        <v>1.309559345245361</v>
+        <v>0.9691764116287231</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -7098,7 +7098,7 @@
         <v>12</v>
       </c>
       <c r="D395">
-        <v>4.379722595214844</v>
+        <v>4.241754055023193</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7112,7 +7112,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D396">
-        <v>-2.178882598876953</v>
+        <v>-2.638044118881226</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7126,7 +7126,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D397">
-        <v>5.042650699615479</v>
+        <v>6.162304878234863</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7140,7 +7140,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D398">
-        <v>5.575972557067871</v>
+        <v>7.123780250549316</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7154,7 +7154,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D399">
-        <v>-0.02199101448059082</v>
+        <v>-0.4307296872138977</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7168,7 +7168,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D400">
-        <v>-0.09840899705886841</v>
+        <v>-0.1869247555732727</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7182,7 +7182,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D401">
-        <v>0.7772834300994873</v>
+        <v>1.196191310882568</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7196,7 +7196,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D402">
-        <v>6.61682653427124</v>
+        <v>5.987594604492188</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7210,7 +7210,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D403">
-        <v>0.1994248926639557</v>
+        <v>-0.3381431698799133</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7224,7 +7224,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D404">
-        <v>4.931645393371582</v>
+        <v>4.724813461303711</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7238,7 +7238,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D405">
-        <v>0.5755811929702759</v>
+        <v>0.5279353857040405</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7252,7 +7252,7 @@
         <v>-3</v>
       </c>
       <c r="D406">
-        <v>-1.620039582252502</v>
+        <v>-1.639650583267212</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7266,7 +7266,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D407">
-        <v>-2.484910488128662</v>
+        <v>-2.844401836395264</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7280,7 +7280,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D408">
-        <v>-0.3557516932487488</v>
+        <v>-0.05030995607376099</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7294,7 +7294,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D409">
-        <v>8.600305557250977</v>
+        <v>7.871026992797852</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7308,7 +7308,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D410">
-        <v>0.8637027144432068</v>
+        <v>0.610466480255127</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7322,7 +7322,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D411">
-        <v>-2.151607036590576</v>
+        <v>-1.475176572799683</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7336,7 +7336,7 @@
         <v>-1.5</v>
       </c>
       <c r="D412">
-        <v>-1.410534262657166</v>
+        <v>-1.003450155258179</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7350,7 +7350,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D413">
-        <v>0.3888683319091797</v>
+        <v>1.336119532585144</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7364,7 +7364,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D414">
-        <v>2.941338062286377</v>
+        <v>4.196261405944824</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7378,7 +7378,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D415">
-        <v>6.762782096862793</v>
+        <v>5.839574337005615</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7392,7 +7392,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D416">
-        <v>1.625841736793518</v>
+        <v>1.529120206832886</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7406,7 +7406,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D417">
-        <v>5.355832099914551</v>
+        <v>4.709362983703613</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7420,7 +7420,7 @@
         <v>5</v>
       </c>
       <c r="D418">
-        <v>2.76613712310791</v>
+        <v>2.990894556045532</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7434,7 +7434,7 @@
         <v>13</v>
       </c>
       <c r="D419">
-        <v>10.52684879302979</v>
+        <v>8.492579460144043</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7448,7 +7448,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D420">
-        <v>1.008357763290405</v>
+        <v>1.372189521789551</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7462,7 +7462,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D421">
-        <v>-5.42006778717041</v>
+        <v>-4.017279624938965</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7476,7 +7476,7 @@
         <v>22</v>
       </c>
       <c r="D422">
-        <v>16.37234687805176</v>
+        <v>15.63749122619629</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7490,7 +7490,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D423">
-        <v>0.506695568561554</v>
+        <v>1.223626732826233</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7504,7 +7504,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D424">
-        <v>0.3903219103813171</v>
+        <v>0.7620162963867188</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7518,7 +7518,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D425">
-        <v>8.366312026977539</v>
+        <v>7.304965972900391</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7532,7 +7532,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D426">
-        <v>1.763206839561462</v>
+        <v>3.178643226623535</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7546,7 +7546,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D427">
-        <v>0.4689558446407318</v>
+        <v>0.4053072333335876</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7560,7 +7560,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D428">
-        <v>2.054378986358643</v>
+        <v>1.239653348922729</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7574,7 +7574,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D429">
-        <v>6.303676605224609</v>
+        <v>5.137247085571289</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7588,7 +7588,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D430">
-        <v>4.305902481079102</v>
+        <v>4.252656936645508</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7602,7 +7602,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D431">
-        <v>7.309755802154541</v>
+        <v>7.380969047546387</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7616,7 +7616,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D432">
-        <v>0.1673104763031006</v>
+        <v>0.009934425354003906</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7630,7 +7630,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D433">
-        <v>-1.804139733314514</v>
+        <v>-1.759836673736572</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7644,7 +7644,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D434">
-        <v>0.07170397043228149</v>
+        <v>0.1451465487480164</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7658,7 +7658,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D435">
-        <v>2.141985416412354</v>
+        <v>1.911599397659302</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7672,7 +7672,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D436">
-        <v>4.671939849853516</v>
+        <v>2.67323899269104</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7686,7 +7686,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D437">
-        <v>0.4659167528152466</v>
+        <v>0.5109854936599731</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7700,7 +7700,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="D438">
-        <v>7.328239917755127</v>
+        <v>7.058568000793457</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7714,7 +7714,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D439">
-        <v>3.836295127868652</v>
+        <v>5.867846488952637</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7728,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="D440">
-        <v>-1.106058120727539</v>
+        <v>-1.190053939819336</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7742,7 +7742,7 @@
         <v>9</v>
       </c>
       <c r="D441">
-        <v>4.648933410644531</v>
+        <v>3.924228668212891</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="D442">
-        <v>0.8665267825126648</v>
+        <v>0.409271627664566</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7770,7 +7770,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D443">
-        <v>3.808567523956299</v>
+        <v>2.406008958816528</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7784,7 +7784,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D444">
-        <v>1.280875205993652</v>
+        <v>2.359474420547485</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7798,7 +7798,7 @@
         <v>6</v>
       </c>
       <c r="D445">
-        <v>3.676005840301514</v>
+        <v>2.389810562133789</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7812,7 +7812,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D446">
-        <v>4.591734409332275</v>
+        <v>4.583248138427734</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7826,7 +7826,7 @@
         <v>-3</v>
       </c>
       <c r="D447">
-        <v>0.4732502698898315</v>
+        <v>0.6184520721435547</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7840,7 +7840,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D448">
-        <v>0.4406060576438904</v>
+        <v>0.3070973455905914</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7854,7 +7854,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D449">
-        <v>-2.972911357879639</v>
+        <v>-2.387850522994995</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7868,7 +7868,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D450">
-        <v>2.172117233276367</v>
+        <v>2.327616453170776</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7882,7 +7882,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D451">
-        <v>4.439144134521484</v>
+        <v>2.266047239303589</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7896,7 +7896,7 @@
         <v>-2</v>
       </c>
       <c r="D452">
-        <v>0.1257379055023193</v>
+        <v>-0.1643919348716736</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7910,7 +7910,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D453">
-        <v>4.906338691711426</v>
+        <v>3.675085306167603</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7924,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="D454">
-        <v>1.442807912826538</v>
+        <v>0.7295942902565002</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7938,7 +7938,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D455">
-        <v>-1.848763585090637</v>
+        <v>-2.408751487731934</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7952,7 +7952,7 @@
         <v>13</v>
       </c>
       <c r="D456">
-        <v>8.25944995880127</v>
+        <v>9.884565353393555</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7966,7 +7966,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D457">
-        <v>4.057504177093506</v>
+        <v>4.572463989257812</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -7980,7 +7980,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D458">
-        <v>-2.268682479858398</v>
+        <v>-1.370974779129028</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -7994,7 +7994,7 @@
         <v>-6.400000095367432</v>
       </c>
       <c r="D459">
-        <v>-2.388177394866943</v>
+        <v>-1.90674901008606</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8008,7 +8008,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D460">
-        <v>2.043646812438965</v>
+        <v>1.606221914291382</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8022,7 +8022,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D461">
-        <v>1.292106032371521</v>
+        <v>0.908039927482605</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8036,7 +8036,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D462">
-        <v>0.6005991697311401</v>
+        <v>0.5542722940444946</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8050,7 +8050,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D463">
-        <v>-0.2648420333862305</v>
+        <v>-0.2135408520698547</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -8064,7 +8064,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D464">
-        <v>2.628666877746582</v>
+        <v>3.115320920944214</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -8078,7 +8078,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D465">
-        <v>4.253443241119385</v>
+        <v>4.183236598968506</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -8092,7 +8092,7 @@
         <v>0.5</v>
       </c>
       <c r="D466">
-        <v>1.770901322364807</v>
+        <v>1.065241575241089</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -8106,7 +8106,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D467">
-        <v>-1.188981890678406</v>
+        <v>-1.201253890991211</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -8120,7 +8120,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D468">
-        <v>0.4664292335510254</v>
+        <v>0.2006238996982574</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -8134,7 +8134,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D469">
-        <v>0.6841232180595398</v>
+        <v>1.559750080108643</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -8148,7 +8148,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D470">
-        <v>3.703786373138428</v>
+        <v>3.25985312461853</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8162,7 +8162,7 @@
         <v>-3.5</v>
       </c>
       <c r="D471">
-        <v>-0.1740241050720215</v>
+        <v>-0.3752921223640442</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8176,7 +8176,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D472">
-        <v>0.03374189138412476</v>
+        <v>0.0156894326210022</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8190,7 +8190,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D473">
-        <v>0.4256056547164917</v>
+        <v>0.3165017366409302</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8204,7 +8204,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D474">
-        <v>3.423447132110596</v>
+        <v>2.53729510307312</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8218,7 +8218,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D475">
-        <v>6.693950176239014</v>
+        <v>6.003371238708496</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8232,7 +8232,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D476">
-        <v>-5.820091247558594</v>
+        <v>-3.992113828659058</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8246,7 +8246,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D477">
-        <v>-1.301805973052979</v>
+        <v>-1.770475149154663</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8260,7 +8260,7 @@
         <v>2.5</v>
       </c>
       <c r="D478">
-        <v>-2.436718463897705</v>
+        <v>-1.664639949798584</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8274,7 +8274,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D479">
-        <v>-1.118997097015381</v>
+        <v>-0.5535643696784973</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8288,7 +8288,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D480">
-        <v>0.02912792563438416</v>
+        <v>0.1710419654846191</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8302,7 +8302,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D481">
-        <v>0.1457668840885162</v>
+        <v>-0.008343219757080078</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8316,7 +8316,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D482">
-        <v>1.929020524024963</v>
+        <v>0.9002230763435364</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8330,7 +8330,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D483">
-        <v>0.7081119418144226</v>
+        <v>0.9610238075256348</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8344,7 +8344,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D484">
-        <v>1.797467947006226</v>
+        <v>2.265978574752808</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8358,7 +8358,7 @@
         <v>36.09999847412109</v>
       </c>
       <c r="D485">
-        <v>17.92219543457031</v>
+        <v>18.57807922363281</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8372,7 +8372,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D486">
-        <v>0.479424387216568</v>
+        <v>0.7684073448181152</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8386,7 +8386,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D487">
-        <v>3.014387607574463</v>
+        <v>2.222976207733154</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8400,7 +8400,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D488">
-        <v>-1.991800665855408</v>
+        <v>-1.246651649475098</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8414,7 +8414,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D489">
-        <v>-1.99285089969635</v>
+        <v>-1.789952516555786</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8428,7 +8428,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D490">
-        <v>-3.063468933105469</v>
+        <v>-3.698167562484741</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8442,7 +8442,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D491">
-        <v>-1.430171132087708</v>
+        <v>1.916595220565796</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8456,7 +8456,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D492">
-        <v>4.700193881988525</v>
+        <v>5.553184509277344</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8470,7 +8470,7 @@
         <v>-3</v>
       </c>
       <c r="D493">
-        <v>-0.3316608667373657</v>
+        <v>0.02787142992019653</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8484,7 +8484,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D494">
-        <v>1.734578490257263</v>
+        <v>1.142343521118164</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8498,7 +8498,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D495">
-        <v>-2.233731269836426</v>
+        <v>-1.616254568099976</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8512,7 +8512,7 @@
         <v>0.5</v>
       </c>
       <c r="D496">
-        <v>0.4440023005008698</v>
+        <v>0.5371929407119751</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8526,7 +8526,7 @@
         <v>-2</v>
       </c>
       <c r="D497">
-        <v>-0.000619351863861084</v>
+        <v>-0.1027572751045227</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8540,7 +8540,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D498">
-        <v>0.8748153448104858</v>
+        <v>0.2523579001426697</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8554,7 +8554,7 @@
         <v>13</v>
       </c>
       <c r="D499">
-        <v>0.4732502698898315</v>
+        <v>0.6666503548622131</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8568,7 +8568,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>1.417796730995178</v>
+        <v>2.178177356719971</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8582,7 +8582,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D501">
-        <v>-2.737672328948975</v>
+        <v>-2.17221999168396</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8596,7 +8596,7 @@
         <v>8.5</v>
       </c>
       <c r="D502">
-        <v>8.767085075378418</v>
+        <v>8.021158218383789</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8610,7 +8610,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D503">
-        <v>2.686342716217041</v>
+        <v>2.407108783721924</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8624,7 +8624,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D504">
-        <v>3.567775726318359</v>
+        <v>3.862648248672485</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8638,7 +8638,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D505">
-        <v>1.83787214756012</v>
+        <v>1.752894163131714</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8652,7 +8652,7 @@
         <v>6.5</v>
       </c>
       <c r="D506">
-        <v>1.022253513336182</v>
+        <v>1.486321926116943</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8666,7 +8666,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D507">
-        <v>1.256962895393372</v>
+        <v>1.656619906425476</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8680,7 +8680,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D508">
-        <v>2.0383620262146</v>
+        <v>1.84861421585083</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8694,7 +8694,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D509">
-        <v>1.245514988899231</v>
+        <v>1.684931755065918</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8708,7 +8708,7 @@
         <v>3</v>
       </c>
       <c r="D510">
-        <v>0.4732502698898315</v>
+        <v>0.5188930630683899</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8722,7 +8722,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D511">
-        <v>-2.371208190917969</v>
+        <v>-2.357524633407593</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8736,7 +8736,7 @@
         <v>32.5</v>
       </c>
       <c r="D512">
-        <v>18.24445152282715</v>
+        <v>16.66703796386719</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8750,7 +8750,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D513">
-        <v>0.98711097240448</v>
+        <v>1.412058591842651</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8764,7 +8764,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D514">
-        <v>-2.142959594726562</v>
+        <v>-1.15554666519165</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8778,7 +8778,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D515">
-        <v>-1.22967255115509</v>
+        <v>-1.524044752120972</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8792,7 +8792,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D516">
-        <v>1.13264799118042</v>
+        <v>0.6689033508300781</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8806,7 +8806,7 @@
         <v>-1.5</v>
       </c>
       <c r="D517">
-        <v>0.5700824856758118</v>
+        <v>0.7625832557678223</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8820,7 +8820,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D518">
-        <v>-0.85050368309021</v>
+        <v>-1.9277503490448</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8834,7 +8834,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D519">
-        <v>-6.402712821960449</v>
+        <v>-5.151915550231934</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8848,7 +8848,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D520">
-        <v>4.653221130371094</v>
+        <v>2.638558864593506</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8862,7 +8862,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D521">
-        <v>10.89424228668213</v>
+        <v>10.41581153869629</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8876,7 +8876,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D522">
-        <v>-0.4592753648757935</v>
+        <v>-0.07980149984359741</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8890,7 +8890,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D523">
-        <v>8.739232063293457</v>
+        <v>8.947304725646973</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8904,7 +8904,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D524">
-        <v>0.3984559178352356</v>
+        <v>0.61292564868927</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8918,7 +8918,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="D525">
-        <v>9.05595874786377</v>
+        <v>9.264323234558105</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8932,7 +8932,7 @@
         <v>-3</v>
       </c>
       <c r="D526">
-        <v>-2.46113920211792</v>
+        <v>-2.51716160774231</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8946,7 +8946,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D527">
-        <v>4.531075954437256</v>
+        <v>5.664960861206055</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8960,7 +8960,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D528">
-        <v>4.046708106994629</v>
+        <v>3.418185949325562</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8974,7 +8974,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D529">
-        <v>-0.07285767793655396</v>
+        <v>0.2435258030891418</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8988,7 +8988,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D530">
-        <v>-0.1868759393692017</v>
+        <v>-0.5198350548744202</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9002,7 +9002,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D531">
-        <v>-2.848575592041016</v>
+        <v>-3.444685220718384</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9016,7 +9016,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D532">
-        <v>0.3229276537895203</v>
+        <v>0.07752180099487305</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9030,7 +9030,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D533">
-        <v>-1.209339022636414</v>
+        <v>-0.9084761738777161</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9044,7 +9044,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D534">
-        <v>0.5049813389778137</v>
+        <v>1.320544600486755</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9058,7 +9058,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D535">
-        <v>6.502435684204102</v>
+        <v>6.194577217102051</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9072,7 +9072,7 @@
         <v>26</v>
       </c>
       <c r="D536">
-        <v>14.07245349884033</v>
+        <v>15.09690570831299</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9086,7 +9086,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D537">
-        <v>5.556583404541016</v>
+        <v>4.133759021759033</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9100,7 +9100,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D538">
-        <v>0.7568111419677734</v>
+        <v>1.203176617622375</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9114,7 +9114,7 @@
         <v>15.89999961853027</v>
       </c>
       <c r="D539">
-        <v>10.0622091293335</v>
+        <v>9.554699897766113</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9128,7 +9128,7 @@
         <v>27.5</v>
       </c>
       <c r="D540">
-        <v>12.80862903594971</v>
+        <v>11.54977798461914</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9142,7 +9142,7 @@
         <v>6</v>
       </c>
       <c r="D541">
-        <v>8.516142845153809</v>
+        <v>-1.5294349193573</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9156,7 +9156,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D542">
-        <v>3.336988925933838</v>
+        <v>2.157837867736816</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9170,7 +9170,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D543">
-        <v>0.5064070820808411</v>
+        <v>0.07175749540328979</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9184,7 +9184,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D544">
-        <v>0.5335882306098938</v>
+        <v>0.9859862327575684</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9198,7 +9198,7 @@
         <v>1.5</v>
       </c>
       <c r="D545">
-        <v>-0.4861452579498291</v>
+        <v>-1.04541277885437</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9212,7 +9212,7 @@
         <v>-9.100000381469727</v>
       </c>
       <c r="D546">
-        <v>-0.6848143339157104</v>
+        <v>-0.3530755639076233</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9226,7 +9226,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D547">
-        <v>6.304489612579346</v>
+        <v>6.297867774963379</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9240,7 +9240,7 @@
         <v>-8.600000381469727</v>
       </c>
       <c r="D548">
-        <v>-2.592319965362549</v>
+        <v>-1.845427274703979</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9254,7 +9254,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D549">
-        <v>-0.7170435190200806</v>
+        <v>-0.1180238723754883</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9268,7 +9268,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D550">
-        <v>2.58860969543457</v>
+        <v>2.757387399673462</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9282,7 +9282,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D551">
-        <v>2.605019569396973</v>
+        <v>1.964483737945557</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9296,7 +9296,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D552">
-        <v>6.276507377624512</v>
+        <v>6.010870933532715</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9310,7 +9310,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D553">
-        <v>-1.973264336585999</v>
+        <v>-0.9167171120643616</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9324,7 +9324,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D554">
-        <v>-0.4485984444618225</v>
+        <v>-0.1171278953552246</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9338,7 +9338,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D555">
-        <v>0.42840176820755</v>
+        <v>0.2281838059425354</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9352,7 +9352,7 @@
         <v>2</v>
       </c>
       <c r="D556">
-        <v>-0.8323023319244385</v>
+        <v>0.02100026607513428</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9366,7 +9366,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D557">
-        <v>-0.9017467498779297</v>
+        <v>-0.7832644581794739</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9380,7 +9380,7 @@
         <v>6</v>
       </c>
       <c r="D558">
-        <v>4.685388565063477</v>
+        <v>4.105262279510498</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9394,7 +9394,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D559">
-        <v>2.501378536224365</v>
+        <v>2.275799989700317</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9408,7 +9408,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D560">
-        <v>-0.1988630890846252</v>
+        <v>-0.4320760369300842</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -9422,7 +9422,7 @@
         <v>-4</v>
       </c>
       <c r="D561">
-        <v>0.1701083183288574</v>
+        <v>0.2938828766345978</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -9436,7 +9436,7 @@
         <v>-2.5</v>
       </c>
       <c r="D562">
-        <v>-2.368700981140137</v>
+        <v>-2.091094017028809</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -9450,7 +9450,7 @@
         <v>1.5</v>
       </c>
       <c r="D563">
-        <v>0.7365903854370117</v>
+        <v>0.7126262784004211</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -9464,7 +9464,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D564">
-        <v>-2.446091175079346</v>
+        <v>-1.863735437393188</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -9478,7 +9478,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D565">
-        <v>0.8586386442184448</v>
+        <v>0.5462948083877563</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -9492,7 +9492,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D566">
-        <v>-0.3898947238922119</v>
+        <v>0.2939316630363464</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -9506,7 +9506,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D567">
-        <v>6.15087890625</v>
+        <v>6.13409423828125</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -9520,7 +9520,7 @@
         <v>5.5</v>
       </c>
       <c r="D568">
-        <v>4.78568172454834</v>
+        <v>4.239362239837646</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -9534,7 +9534,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D569">
-        <v>0.01433652639389038</v>
+        <v>1.005491375923157</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -9548,7 +9548,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D570">
-        <v>3.54042387008667</v>
+        <v>2.841838121414185</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -9562,7 +9562,7 @@
         <v>4</v>
       </c>
       <c r="D571">
-        <v>2.331549644470215</v>
+        <v>1.944132328033447</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -9576,7 +9576,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D572">
-        <v>0.2973069846630096</v>
+        <v>0.2717090249061584</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -9590,7 +9590,7 @@
         <v>-1.5</v>
       </c>
       <c r="D573">
-        <v>3.905386924743652</v>
+        <v>4.082466602325439</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -9604,7 +9604,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D574">
-        <v>4.349178314208984</v>
+        <v>4.537663459777832</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -9618,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="D575">
-        <v>0.2528570890426636</v>
+        <v>-0.288343608379364</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -9632,7 +9632,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D576">
-        <v>2.529221057891846</v>
+        <v>2.992302179336548</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -9646,7 +9646,7 @@
         <v>-0.5</v>
       </c>
       <c r="D577">
-        <v>-0.373889148235321</v>
+        <v>-0.327680230140686</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -9660,7 +9660,7 @@
         <v>0.5</v>
       </c>
       <c r="D578">
-        <v>3.285290718078613</v>
+        <v>3.138690948486328</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -9674,7 +9674,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>3.4413161277771</v>
+        <v>1.115530610084534</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -9688,7 +9688,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D580">
-        <v>16.62668800354004</v>
+        <v>17.16943740844727</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -9702,7 +9702,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D581">
-        <v>1.117759346961975</v>
+        <v>1.175392150878906</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -9716,7 +9716,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D582">
-        <v>0.4370905160903931</v>
+        <v>0.5834632515907288</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -9730,7 +9730,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D583">
-        <v>0.4127365946769714</v>
+        <v>0.1642418205738068</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -9744,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="D584">
-        <v>-0.3309795260429382</v>
+        <v>1.343684911727905</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -9758,7 +9758,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D585">
-        <v>-0.5087493658065796</v>
+        <v>-0.3781132102012634</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -9772,7 +9772,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D586">
-        <v>4.837058067321777</v>
+        <v>4.926188468933105</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -9786,7 +9786,7 @@
         <v>2</v>
       </c>
       <c r="D587">
-        <v>1.862246155738831</v>
+        <v>1.973002433776855</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -9800,7 +9800,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D588">
-        <v>-1.973991990089417</v>
+        <v>-1.969487905502319</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -9814,7 +9814,7 @@
         <v>10</v>
       </c>
       <c r="D589">
-        <v>4.633280754089355</v>
+        <v>1.822692155838013</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -9828,7 +9828,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D590">
-        <v>1.552788853645325</v>
+        <v>1.428003787994385</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -9842,7 +9842,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D591">
-        <v>1.094598770141602</v>
+        <v>0.6552824378013611</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -9856,7 +9856,7 @@
         <v>34.59999847412109</v>
       </c>
       <c r="D592">
-        <v>29.95947074890137</v>
+        <v>35.18292999267578</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -9870,7 +9870,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D593">
-        <v>-5.274982452392578</v>
+        <v>-6.091146945953369</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -9884,7 +9884,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D594">
-        <v>-1.276913046836853</v>
+        <v>-0.7303966879844666</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -9898,7 +9898,7 @@
         <v>0.5</v>
       </c>
       <c r="D595">
-        <v>1.264639377593994</v>
+        <v>2.589166879653931</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -9912,7 +9912,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D596">
-        <v>-2.9202880859375</v>
+        <v>-3.137239694595337</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -9926,7 +9926,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D597">
-        <v>-0.9610471725463867</v>
+        <v>-1.390429735183716</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -9940,7 +9940,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D598">
-        <v>3.136518001556396</v>
+        <v>2.438775539398193</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -9954,7 +9954,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D599">
-        <v>3.59174633026123</v>
+        <v>4.223479747772217</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -9968,7 +9968,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D600">
-        <v>-1.592911601066589</v>
+        <v>-1.335713148117065</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -9982,7 +9982,7 @@
         <v>-12.19999980926514</v>
       </c>
       <c r="D601">
-        <v>-2.366479396820068</v>
+        <v>-0.0781669020652771</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -9996,7 +9996,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D602">
-        <v>0.6567751169204712</v>
+        <v>0.5836134552955627</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10010,7 +10010,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D603">
-        <v>-0.9436380863189697</v>
+        <v>-0.8493703007698059</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10024,7 +10024,7 @@
         <v>1</v>
       </c>
       <c r="D604">
-        <v>0.4411895871162415</v>
+        <v>0.5682106018066406</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -10038,7 +10038,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D605">
-        <v>4.043998241424561</v>
+        <v>3.819207191467285</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -10052,7 +10052,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D606">
-        <v>-0.2303271293640137</v>
+        <v>-0.176976203918457</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -10066,7 +10066,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D607">
-        <v>2.247640609741211</v>
+        <v>0.9482197165489197</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -10080,7 +10080,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D608">
-        <v>4.26078462600708</v>
+        <v>5.32411003112793</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -10094,7 +10094,7 @@
         <v>-0.5</v>
       </c>
       <c r="D609">
-        <v>0.1804277896881104</v>
+        <v>-0.1397466063499451</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -10108,7 +10108,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D610">
-        <v>3.170188903808594</v>
+        <v>2.407915830612183</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -10122,7 +10122,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D611">
-        <v>3.076591491699219</v>
+        <v>3.696861267089844</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -10136,7 +10136,7 @@
         <v>3</v>
       </c>
       <c r="D612">
-        <v>1.087425231933594</v>
+        <v>0.3882679343223572</v>
       </c>
     </row>
   </sheetData>
